--- a/data/trans_orig/P41C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo en 2023</t>
+          <t>Población con dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1901</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1075</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3435</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121583</t>
+          <t>121838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52436</t>
+          <t>52445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113644</t>
+          <t>113530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123182</t>
+          <t>123139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>62004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72269</t>
+          <t>72831</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64382</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>72628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130832</t>
+          <t>130874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143205</t>
+          <t>143498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53173</t>
+          <t>48644</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>60652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67995</t>
+          <t>68367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115419</t>
+          <t>116859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132801</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49978</t>
+          <t>48362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65056</t>
+          <t>65297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116762</t>
+          <t>116927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121112</t>
+          <t>121107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>58502</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63867</t>
+          <t>63851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130529</t>
+          <t>130711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136345</t>
+          <t>136339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14813</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>27389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91132</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102574</t>
+          <t>102596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137842</t>
+          <t>138031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148227</t>
+          <t>148189</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233140</t>
+          <t>231857</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>248416</t>
+          <t>248476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9553</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>888</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>367630</t>
+          <t>367253</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126026</t>
+          <t>125937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>134128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>499229</t>
+          <t>499657</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>518870</t>
+          <t>519112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>75386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>835103</t>
+          <t>835387</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>868457</t>
+          <t>869304</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>674208</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1498957</t>
+          <t>1499311</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1541807</t>
+          <t>1539506</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64896</t>
+          <t>71375</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>124478</t>
+          <t>131140</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121838</t>
+          <t>128964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>72407</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125553</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>59112</t>
+          <t>64048</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52445</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>63498</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>59048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>120168</t>
+          <t>127545</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113530</t>
+          <t>120837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123139</t>
+          <t>130829</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>66940</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>124377</t>
+          <t>132279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19586</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68754</t>
+          <t>67693</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72831</t>
+          <t>71706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69293</t>
+          <t>70477</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>65609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72628</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>138047</t>
+          <t>138171</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130874</t>
+          <t>130919</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143498</t>
+          <t>143555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75104</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75356</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150460</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>62627</t>
+          <t>70962</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48644</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65382</t>
+          <t>73073</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60652</t>
+          <t>68177</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68367</t>
+          <t>75834</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>128009</t>
+          <t>144034</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116859</t>
+          <t>130545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132969</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>75884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>77531</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136605</t>
+          <t>153414</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1788</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52161</t>
+          <t>59683</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>56177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,27 +2245,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>67668</t>
+          <t>76262</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65297</t>
+          <t>73598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>119830</t>
+          <t>135945</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116927</t>
+          <t>132671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121107</t>
+          <t>137398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52855</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68604</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>137733</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>137733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>137733</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>62349</t>
+          <t>63939</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58502</t>
+          <t>59787</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63851</t>
+          <t>65468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>134855</t>
+          <t>138980</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130711</t>
+          <t>135114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136339</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72506</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64491</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>136997</t>
+          <t>141127</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>16455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17347</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>11821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>97986</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>91547</t>
+          <t>101785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102596</t>
+          <t>115384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>143912</t>
+          <t>169260</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138031</t>
+          <t>162557</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>148189</t>
+          <t>173483</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>241899</t>
+          <t>279989</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231857</t>
+          <t>271088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>248476</t>
+          <t>287068</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>119877</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>119877</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>119877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>179012</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>259246</t>
+          <t>298889</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,67 +3126,67 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10898</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4295</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1451</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9642</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8517</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -3239,69 +3239,69 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>380199</t>
+          <t>159278</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>367253</t>
+          <t>152316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>162815</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>153945</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>147754</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>156900</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>131284</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>125937</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>134128</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>309</t>
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>511483</t>
+          <t>313223</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>499657</t>
+          <t>304513</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>519112</t>
+          <t>318409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>384421</t>
+          <t>163998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>135579</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>135579</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>135579</t>
+          <t>158652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>322650</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>42269</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>46801</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75386</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>852928</t>
+          <t>667199</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>835387</t>
+          <t>649949</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>869304</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1518768</t>
+          <t>1409027</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1499311</t>
+          <t>1389789</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1539506</t>
+          <t>1422551</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
